--- a/opportunities/tracker.xlsx
+++ b/opportunities/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coding\apps\flutter\fairbanks\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0885F0C1-4690-4D96-ACFF-492CDA245A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A6DA81-3109-4107-A11A-1D8BAEE1207C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/opportunities/tracker.xlsx
+++ b/opportunities/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coding\apps\flutter\fairbanks\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A6DA81-3109-4107-A11A-1D8BAEE1207C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A116C12-FFE1-4627-9083-7A8933925C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="Scan Notes" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Opportunities!$A$1:$I$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Opportunities!$A$1:$I$6</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="82">
   <si>
     <t>Project Title</t>
   </si>
@@ -111,21 +111,6 @@
   </si>
   <si>
     <t>unknown</t>
-  </si>
-  <si>
-    <t>DPI Safeguards Accelerator (UN ODET / UNDP)</t>
-  </si>
-  <si>
-    <t>https://www.dpi-safeguards.org/accelerator</t>
-  </si>
-  <si>
-    <t>Cohort programme helping partners embed practical safeguards into active Digital Public Infrastructure. NGO pathway for Uganda: issue-specific work on FairBanks FCHIP (consent/data use, offline inclusion, grievance). Catalytic grant up to USD 70,000 over 6-9 months, plus tools and peer learning. Stage 1 Airtable screening; Stage 2 needs government letter if longlisted. FairBanks submitted as community-based health operator with live FCHIP MVP.</t>
-  </si>
-  <si>
-    <t>30 July 2026</t>
-  </si>
-  <si>
-    <t>applications/dpi-safeguards</t>
   </si>
   <si>
     <t>U.S. Dept of State — Uganda Health System MOU (up to $60M)</t>
@@ -423,7 +408,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -481,9 +466,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -826,7 +808,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="42.1796875" customWidth="1"/>
@@ -951,90 +933,90 @@
       </c>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:9" ht="169.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:9" ht="156.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="92.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H6" s="15">
+        <v>46225</v>
+      </c>
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" spans="1:9" ht="117" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="14">
-        <v>46232</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="156.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="92.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="H7" s="19">
+        <v>46225</v>
+      </c>
+      <c r="I7" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="15">
-        <v>46225</v>
-      </c>
-      <c r="I7" s="4"/>
-    </row>
-    <row r="8" spans="1:9" ht="110" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:9" ht="117" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
         <v>44</v>
       </c>
@@ -1045,7 +1027,7 @@
         <v>46</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E8" s="18" t="s">
         <v>20</v>
@@ -1060,38 +1042,10 @@
         <v>46225</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="92.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="19">
-        <v>46225</v>
-      </c>
-      <c r="I9" s="16" t="s">
-        <v>52</v>
-      </c>
-    </row>
+    </row>
+    <row r="9" spans="1:9" ht="92.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="1:9" ht="92.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="11" spans="1:9" ht="92.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:9" ht="92.25" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -1104,16 +1058,14 @@
     <row r="19" ht="92.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="20" ht="92.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="21" ht="92.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" ht="92.25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <autoFilter ref="A1:I7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="B3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="B4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="B5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="B6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="B7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="B5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="B6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
@@ -1132,138 +1084,138 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="65" x14ac:dyDescent="0.35">
       <c r="A16" s="20" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/opportunities/tracker.xlsx
+++ b/opportunities/tracker.xlsx
@@ -18,10 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -109,7 +108,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -147,12 +146,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -218,7 +231,13 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -624,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="42.1796875" customWidth="1" min="1" max="3"/>
@@ -892,7 +911,7 @@
           <t>Submitted</t>
         </is>
       </c>
-      <c r="H6" s="23" t="n">
+      <c r="H6" s="24" t="n">
         <v>46243</v>
       </c>
       <c r="I6" s="16" t="inlineStr">
@@ -1032,7 +1051,49 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="92.25" customHeight="1"/>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>CDC - Strengthening Global Health Security detect/notify/respond globally (CDC-RFA-JG-26-0056)</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>https://simpler.grants.gov/opportunity/8454e463-cd43-4d0d-97a2-8a4310e0ce6b</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t>CDC cooperative agreement (93.318) to strengthen country capacity to detect, notify, and respond to outbreaks globally via MoH partnerships. Year 1 pool about USD 24M; 4-8 awards; Component 1 ceiling USD 3M. For-profit and foreign entities eligible; Uganda local partner +10 points. FairBanks Year 1 Uganda-primary with FCHIP last-mile surveillance under MoH. Confirm multi-country LOIs and SAM/UEI before submit. Deadline 14 August 2026.</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>14 August 2026 (11:59 p.m. ET)</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>Multi-gender (all genders)</t>
+        </is>
+      </c>
+      <c r="F10" s="25" t="inlineStr">
+        <is>
+          <t>Drafting</t>
+        </is>
+      </c>
+      <c r="G10" s="25" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H10" s="25" t="inlineStr"/>
+      <c r="I10" s="25" t="inlineStr">
+        <is>
+          <t>applications/cdc-ghs-global</t>
+        </is>
+      </c>
+    </row>
     <row r="11" ht="92.25" customHeight="1"/>
     <row r="12" ht="92.25" customHeight="1"/>
     <row r="13" ht="92.25" customHeight="1"/>

--- a/opportunities/tracker.xlsx
+++ b/opportunities/tracker.xlsx
@@ -18,9 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -1052,43 +1053,45 @@
       </c>
     </row>
     <row r="10" ht="90" customHeight="1">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>CDC - Strengthening Global Health Security detect/notify/respond globally (CDC-RFA-JG-26-0056)</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>https://simpler.grants.gov/opportunity/8454e463-cd43-4d0d-97a2-8a4310e0ce6b</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
-        <is>
-          <t>CDC cooperative agreement (93.318) to strengthen country capacity to detect, notify, and respond to outbreaks globally via MoH partnerships. Year 1 pool about USD 24M; 4-8 awards; Component 1 ceiling USD 3M. For-profit and foreign entities eligible; Uganda local partner +10 points. FairBanks Year 1 Uganda-primary with FCHIP last-mile surveillance under MoH. Confirm multi-country LOIs and SAM/UEI before submit. Deadline 14 August 2026.</t>
-        </is>
-      </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>CDC cooperative agreement (93.318) to strengthen country capacity to detect, notify, and respond to outbreaks globally via MoH partnerships. Year 1 pool about USD 24M; 4-8 awards; Component 1 ceiling USD 3M. For-profit and foreign entities eligible; Uganda local partner +10 points. FairBanks submitted Year 1 Uganda-primary ask USD 7.5M (Component 1 USD 3.0M core; Components 2-5 ABU USD 4.5M) with FCHIP last-mile surveillance under MoH.</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>14 August 2026 (11:59 p.m. ET)</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>Multi-gender (all genders)</t>
         </is>
       </c>
-      <c r="F10" s="25" t="inlineStr">
-        <is>
-          <t>Drafting</t>
-        </is>
-      </c>
-      <c r="G10" s="25" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="H10" s="25" t="inlineStr"/>
-      <c r="I10" s="25" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="n">
+        <v>46246</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
         <is>
           <t>applications/cdc-ghs-global</t>
         </is>
@@ -1125,7 +1128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1153,7 +1156,7 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>2026-08-09 (added CDC-RFA-JG-26-0054 submission)</t>
+          <t>2026-08-12 (marked CDC-RFA-JG-26-0056 submitted)</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1324,7 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>2026-08-09: Submitted CDC-RFA-JG-26-0054 Uganda GHS cooperative agreement via Grants.gov (applications/cdc-uganda-ghs; Year 1 ask USD 3.3M). Marked Complete / Submitted. 2026-07-22: Submitted Jay Shetty strategic partnership pack (applications/jayshetty) and Yunus Centre social business partnership pack (applications/yunus). Both marked Complete / Submitted in Opportunities.</t>
+          <t>2026-08-12: Submitted CDC-RFA-JG-26-0056 global GHS detect/notify/respond via Grants.gov (https://simpler.grants.gov/opportunity/8454e463-cd43-4d0d-97a2-8a4310e0ce6b; applications/cdc-ghs-global; Year 1 ask USD 7.5M). Marked Complete / Submitted. 2026-08-09: Submitted CDC-RFA-JG-26-0054 Uganda GHS cooperative agreement via Grants.gov (applications/cdc-uganda-ghs; Year 1 ask USD 3.3M). Marked Complete / Submitted. 2026-07-22: Submitted Jay Shetty strategic partnership pack (applications/jayshetty) and Yunus Centre social business partnership pack (applications/yunus). Both marked Complete / Submitted in Opportunities.</t>
         </is>
       </c>
     </row>
@@ -1346,6 +1349,18 @@
       <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Submitted 2026-08-09 via Grants.gov (opportunity 360339). Pack: applications/cdc-uganda-ghs. Deadline was 14 August 2026, 11:59 p.m. ET. Year 1 federal ask USD 3,300,000 across four SF-424A component rows (Core GHS plus contingency). Local partner preference requested.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CDC Global GHS (CDC-RFA-JG-26-0056)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Submitted 2026-08-12 via Grants.gov / Simpler.Grants.gov opportunity 8454e463-cd43-4d0d-97a2-8a4310e0ce6b. Pack: applications/cdc-ghs-global. Deadline 14 August 2026, 11:59 p.m. ET. Year 1 federal ask USD 7,500,000 (C1 USD 3.0M core; C2-C5 ABU USD 4.5M). Local partner preference requested.</t>
         </is>
       </c>
     </row>
